--- a/Assets/Excel/WeaponConfig.xlsx
+++ b/Assets/Excel/WeaponConfig.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23100" windowHeight="11730" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="weapon" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,33 +11,364 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="weapon_type" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rarity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="substat" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refine" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="20">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -46,15 +376,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -407,7 +1027,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -418,7 +1037,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
+  <cols>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="19.6363636363636" customWidth="1" min="5" max="5"/>
+    <col width="10.6363636363636" customWidth="1" min="6" max="6"/>
+    <col width="11.8181818181818" customWidth="1" min="7" max="7"/>
+    <col width="12.9090909090909" customWidth="1" min="8" max="8"/>
+    <col width="11.8181818181818" customWidth="1" min="9" max="10"/>
+    <col width="10.6363636363636" customWidth="1" min="11" max="11"/>
+    <col width="47.8181818181818" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -572,7 +1202,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>类型(见枚举)</t>
+          <t>类型(1=长刃2=迅刀3=佩枪4=臂铠5=音感仪)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -634,7 +1264,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -642,33 +1272,33 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>33.1</v>
+        <v>24.3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>星之指引</t>
+          <t>逐星</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>施放战技后攻击提升{0}%,持续{1}秒,最多{2}层</t>
+          <t>全属性伤害加成提升{0}%。附加震谐·偏移或聚爆效应时，共鸣解放伤害无视目标{1}%防御，无视目标{2}%热熔抗性，持续8秒。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12;10;3|15;10;3|18;12;4|21;12;4|24;15;5</t>
+          <t>12;32;10|15;40;15|18;48;20|21;56;25|24;64;30</t>
         </is>
       </c>
     </row>
@@ -729,8 +1359,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -806,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="5">
@@ -820,10 +1450,10 @@
         <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="D5" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6">
@@ -834,10 +1464,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="7">
@@ -848,10 +1478,10 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>268</v>
+        <v>335</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="8">
@@ -862,10 +1492,10 @@
         <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>340</v>
+        <v>406</v>
       </c>
       <c r="D8" t="n">
-        <v>19.9</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="9">
@@ -876,10 +1506,10 @@
         <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>414</v>
+        <v>476</v>
       </c>
       <c r="D9" t="n">
-        <v>23.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -890,10 +1520,10 @@
         <v>80</v>
       </c>
       <c r="C10" t="n">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="D10" t="n">
-        <v>27</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +1534,94 @@
         <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="D11" t="n">
-        <v>33.1</v>
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>60</v>
+      </c>
+      <c r="C12" t="n">
+        <v>406</v>
+      </c>
+      <c r="D12" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B13" t="n">
+        <v>70</v>
+      </c>
+      <c r="C13" t="n">
+        <v>445</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>70</v>
+      </c>
+      <c r="C14" t="n">
+        <v>476</v>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80</v>
+      </c>
+      <c r="C15" t="n">
+        <v>516</v>
+      </c>
+      <c r="D15" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80</v>
+      </c>
+      <c r="C16" t="n">
+        <v>547</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90</v>
+      </c>
+      <c r="C17" t="n">
+        <v>587</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24.3</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +1636,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1006,7 +1720,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>近远程</t>
+          <t>近远程(1=近战2=远程)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1026,12 +1740,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>单手剑</t>
+          <t>长刃</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sword</t>
+          <t>Blade</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1050,22 +1764,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>双手剑</t>
+          <t>迅刀</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Claymore</t>
+          <t>Sword</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -1074,22 +1788,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>长枪</t>
+          <t>佩枪</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spear</t>
+          <t>Pistol</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1098,22 +1812,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>法器</t>
+          <t>臂铠</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Catalyst</t>
+          <t>Gauntlet</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
@@ -1122,19 +1836,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>弓</t>
+          <t>音感仪</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Rectifier</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -1152,7 +1866,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
+  <cols>
+    <col width="17.3636363636364" customWidth="1" min="5" max="5"/>
+    <col width="19.6363636363636" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1371,33 +2089,307 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>NameEN</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>IsPercent</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ShortName</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>属性ID</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>属性名</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>英文名</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>百分比标记</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>简称</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>攻击力%</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AtkPercent</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>攻击%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>防御力%</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DefPercent</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>防御%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>生命值%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HpPercent</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>生命%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>暴击率%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>暴击</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>暴击伤害%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CritDmg</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>爆伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>共鸣效率%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ResonanceEfficiency</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>充能</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>攻击力</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>暴击率</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>暴击</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>WeaponId</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Rank</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>NameEN</t>
+          <t>EffectName</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>IsPercent</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ShortName</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
@@ -1409,211 +2401,280 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>属性ID</t>
+          <t>武器ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>属性名</t>
+          <t>精炼阶数(1-5)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>英文名</t>
+          <t>效果名</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>百分比标记</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>简称</t>
+          <t>数值(%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>攻击力%</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AtkPercent</t>
+          <t>全属性伤害加成</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>攻击%</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>防御力%</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DefPercent</t>
+          <t>全属性伤害加成</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>防御%</t>
-        </is>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>生命值%</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HpPercent</t>
+          <t>全属性伤害加成</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>生命%</t>
-        </is>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>暴击率%</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CritRate</t>
+          <t>全属性伤害加成</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>暴击</t>
-        </is>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B8" t="n">
         <v>5</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>暴击伤害%</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CritDmg</t>
+          <t>全属性伤害加成</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>爆伤</t>
-        </is>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>元素充能%</t>
-        </is>
+        <v>1001</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EnergyRecharge</t>
+          <t>无视防御</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>充能</t>
-        </is>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>元素精通</t>
-        </is>
+        <v>1001</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ElementMastery</t>
+          <t>无视防御</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>精通</t>
-        </is>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>无视防御</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>无视防御</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>无视防御</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>无视热熔抗性</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>无视热熔抗性</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>无视热熔抗性</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>无视热熔抗性</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>无视热熔抗性</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
